--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BAXI Manresa.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BAXI Manresa.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>43.2711</v>
+        <v>61.475</v>
       </c>
       <c r="E2" t="n">
-        <v>43.2616</v>
+        <v>58.3651</v>
       </c>
       <c r="F2" t="n">
-        <v>0.009500000000000175</v>
+        <v>3.109599999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8819999999999992</v>
+        <v>-0.6277999999999992</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7098</v>
+        <v>3.3533</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.8278</v>
+        <v>-3.981400000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>22.8851</v>
+        <v>25.4508</v>
       </c>
       <c r="K2" t="n">
-        <v>13.7594</v>
+        <v>16.0278</v>
       </c>
       <c r="L2" t="n">
-        <v>9.1258</v>
+        <v>9.423</v>
       </c>
       <c r="M2" t="n">
-        <v>-22.0031</v>
+        <v>-26.0785</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.0494</v>
+        <v>-12.6745</v>
       </c>
       <c r="O2" t="n">
-        <v>-10.9534</v>
+        <v>-13.4043</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6294</v>
+        <v>7.511999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-27.9007</v>
+        <v>-36.1938</v>
       </c>
       <c r="R2" t="n">
-        <v>31.5299</v>
+        <v>43.7052</v>
       </c>
       <c r="S2" t="n">
-        <v>16.8616</v>
+        <v>30.4718</v>
       </c>
       <c r="T2" t="n">
-        <v>12.7968</v>
+        <v>24.0227</v>
       </c>
       <c r="U2" t="n">
-        <v>4.065</v>
+        <v>6.4492</v>
       </c>
       <c r="V2" t="n">
-        <v>21.898</v>
+        <v>24.119</v>
       </c>
       <c r="W2" t="n">
-        <v>35.48</v>
+        <v>45.0849</v>
       </c>
       <c r="X2" t="n">
-        <v>-13.5819</v>
+        <v>-20.9659</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>26.5742</v>
+        <v>29.4268</v>
       </c>
       <c r="E3" t="n">
-        <v>30.9047</v>
+        <v>30.7167</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.330300000000001</v>
+        <v>-1.2903</v>
       </c>
       <c r="G3" t="n">
-        <v>20.263</v>
+        <v>24.5472</v>
       </c>
       <c r="H3" t="n">
-        <v>19.2674</v>
+        <v>22.2361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9955999999999998</v>
+        <v>2.3111</v>
       </c>
       <c r="J3" t="n">
-        <v>35.3425</v>
+        <v>40.646</v>
       </c>
       <c r="K3" t="n">
-        <v>28.0656</v>
+        <v>32.3797</v>
       </c>
       <c r="L3" t="n">
-        <v>7.2768</v>
+        <v>8.266299999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-15.0796</v>
+        <v>-16.0992</v>
       </c>
       <c r="N3" t="n">
-        <v>-8.7982</v>
+        <v>-10.1438</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.2814</v>
+        <v>-5.9551</v>
       </c>
       <c r="P3" t="n">
-        <v>17.0124</v>
+        <v>18.2104</v>
       </c>
       <c r="Q3" t="n">
-        <v>-21.5491</v>
+        <v>-27.9987</v>
       </c>
       <c r="R3" t="n">
-        <v>38.5617</v>
+        <v>46.2095</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6098000000000006</v>
+        <v>-1.8195</v>
       </c>
       <c r="T3" t="n">
-        <v>7.1804</v>
+        <v>6.4988</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.7901</v>
+        <v>-8.318300000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-10.091</v>
+        <v>-11.5112</v>
       </c>
       <c r="W3" t="n">
-        <v>9.931100000000001</v>
+        <v>11.5706</v>
       </c>
       <c r="X3" t="n">
-        <v>-20.0221</v>
+        <v>-23.0817</v>
       </c>
     </row>
     <row r="4">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>17.0873</v>
+        <v>24.0078</v>
       </c>
       <c r="E4" t="n">
-        <v>5.868400000000001</v>
+        <v>3.709399999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>11.2191</v>
+        <v>20.2984</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.5075</v>
+        <v>-12.1798</v>
       </c>
       <c r="H4" t="n">
-        <v>-22.6093</v>
+        <v>-22.4668</v>
       </c>
       <c r="I4" t="n">
-        <v>13.1017</v>
+        <v>10.2872</v>
       </c>
       <c r="J4" t="n">
-        <v>18.1126</v>
+        <v>18.765</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.1756</v>
+        <v>1.635399999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>20.2883</v>
+        <v>17.1296</v>
       </c>
       <c r="M4" t="n">
-        <v>-27.6198</v>
+        <v>-30.9448</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.4331</v>
+        <v>-24.1019</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.186700000000001</v>
+        <v>-6.8426</v>
       </c>
       <c r="P4" t="n">
-        <v>23.8175</v>
+        <v>30.9579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-35.8398</v>
+        <v>-42.3398</v>
       </c>
       <c r="R4" t="n">
-        <v>59.6568</v>
+        <v>73.297</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.7493</v>
+        <v>-3.7589</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.482</v>
+        <v>-9.960900000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7327</v>
+        <v>6.201599999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5268</v>
+        <v>8.9884</v>
       </c>
       <c r="W4" t="n">
-        <v>31.0775</v>
+        <v>37.2443</v>
       </c>
       <c r="X4" t="n">
-        <v>-23.5507</v>
+        <v>-28.2561</v>
       </c>
     </row>
     <row r="5">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>9.9527</v>
+        <v>13.4816</v>
       </c>
       <c r="E5" t="n">
-        <v>1.363900000000001</v>
+        <v>2.693000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>8.5886</v>
+        <v>10.7885</v>
       </c>
       <c r="G5" t="n">
-        <v>10.0779</v>
+        <v>13.3238</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9811000000000001</v>
+        <v>-2.627899999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>11.0588</v>
+        <v>15.9516</v>
       </c>
       <c r="J5" t="n">
-        <v>16.246</v>
+        <v>20.3174</v>
       </c>
       <c r="K5" t="n">
-        <v>3.181000000000001</v>
+        <v>3.3889</v>
       </c>
       <c r="L5" t="n">
-        <v>13.065</v>
+        <v>16.9285</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.168200000000001</v>
+        <v>-6.993699999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.1619</v>
+        <v>-6.0167</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0062</v>
+        <v>-0.9768</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9071000000000002</v>
+        <v>3.1866</v>
       </c>
       <c r="Q5" t="n">
-        <v>-26.7663</v>
+        <v>-30.7304</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6738</v>
+        <v>33.917</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.7079</v>
+        <v>-6.8194</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.3528</v>
+        <v>-2.4773</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.3552</v>
+        <v>-4.3424</v>
       </c>
       <c r="V5" t="n">
-        <v>5.6753</v>
+        <v>3.7905</v>
       </c>
       <c r="W5" t="n">
-        <v>14.237</v>
+        <v>15.583</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.561499999999999</v>
+        <v>-11.7926</v>
       </c>
     </row>
     <row r="6">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2536</v>
+        <v>9.026299999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0992</v>
+        <v>6.001600000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1543000000000001</v>
+        <v>3.0246</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.752299999999998</v>
+        <v>-6.6158</v>
       </c>
       <c r="H6" t="n">
-        <v>-10.7479</v>
+        <v>-12.6159</v>
       </c>
       <c r="I6" t="n">
-        <v>3.995699999999999</v>
+        <v>6.000100000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>15.4104</v>
+        <v>15.9152</v>
       </c>
       <c r="K6" t="n">
-        <v>3.94</v>
+        <v>3.9477</v>
       </c>
       <c r="L6" t="n">
-        <v>11.4709</v>
+        <v>11.9674</v>
       </c>
       <c r="M6" t="n">
-        <v>-22.1628</v>
+        <v>-22.5307</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.6878</v>
+        <v>-16.5639</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.475300000000001</v>
+        <v>-5.966799999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>9.754</v>
+        <v>12.0646</v>
       </c>
       <c r="Q6" t="n">
-        <v>-34.025</v>
+        <v>-34.3724</v>
       </c>
       <c r="R6" t="n">
-        <v>43.779</v>
+        <v>46.4373</v>
       </c>
       <c r="S6" t="n">
-        <v>8.4444</v>
+        <v>9.687099999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>12.9753</v>
+        <v>13.7635</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.5313</v>
+        <v>-4.0765</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.1923</v>
+        <v>-6.1094</v>
       </c>
       <c r="W6" t="n">
-        <v>9.7379</v>
+        <v>10.6954</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.9304</v>
+        <v>-16.8047</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1187</v>
+        <v>2.1816</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7387</v>
+        <v>4.6404</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.62</v>
+        <v>-2.4589</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1148</v>
+        <v>1.1571</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7644</v>
+        <v>3.7871</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.649600000000001</v>
+        <v>-2.6298</v>
       </c>
       <c r="J7" t="n">
-        <v>6.9016</v>
+        <v>6.821300000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>5.2359</v>
+        <v>5.1841</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6657</v>
+        <v>1.6374</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.786799999999999</v>
+        <v>-5.6644</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4716</v>
+        <v>-1.3969</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.315300000000001</v>
+        <v>-4.267</v>
       </c>
       <c r="P7" t="n">
-        <v>6.3512</v>
+        <v>6.3736</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R7" t="n">
-        <v>10.2074</v>
+        <v>10.2433</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.2392</v>
+        <v>-3.2477</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8135</v>
+        <v>-0.8057000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.4257</v>
+        <v>-2.4421</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1082</v>
+        <v>-2.1016</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5068</v>
+        <v>2.4946</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.615</v>
+        <v>-4.596</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0554</v>
+        <v>-1.0607</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8797</v>
+        <v>-0.8963</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1757</v>
+        <v>-0.1644</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5396</v>
+        <v>-1.5462</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3881</v>
+        <v>-0.3932</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1515</v>
+        <v>-1.153</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6711</v>
+        <v>-0.6872</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4818</v>
+        <v>-0.4934</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8685</v>
+        <v>-0.859</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1963</v>
+        <v>-0.1974</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0124</v>
+        <v>0.0117</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,55 +1111,55 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2295</v>
+        <v>-1.2314</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9199</v>
+        <v>-1.9273</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6904</v>
+        <v>0.6958</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7662</v>
+        <v>-0.7667999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9235</v>
+        <v>-0.9247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.738</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.738</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03179999999999999</v>
+        <v>-0.02889999999999998</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4536</v>
+        <v>-0.4552</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.009799999999999989</v>
+        <v>-0.009400000000000006</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0514</v>
+        <v>-0.05119999999999998</v>
       </c>
       <c r="U9" t="n">
         <v>0.0418</v>
@@ -1189,67 +1189,67 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8647</v>
+        <v>-2.8518</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5339</v>
+        <v>-1.5424</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3309</v>
+        <v>-1.3093</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7711</v>
+        <v>-1.7625</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2971</v>
+        <v>-0.2986000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.474</v>
+        <v>-1.4638</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9985999999999999</v>
+        <v>-1.0077</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0359</v>
+        <v>-1.045</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7725</v>
+        <v>-0.7547</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7386999999999999</v>
+        <v>0.7463</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6806000000000001</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4536</v>
+        <v>0.4552</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.09160000000000001</v>
+        <v>-0.0908000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5988000000000001</v>
+        <v>0.6035000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6904999999999999</v>
+        <v>-0.6941999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.973500000000001</v>
+        <v>-4.2218</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.138200000000001</v>
+        <v>-8.818999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1648</v>
+        <v>4.597200000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>14.899</v>
+        <v>14.7019</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.2018</v>
+        <v>-5.3865</v>
       </c>
       <c r="I11" t="n">
-        <v>20.1007</v>
+        <v>20.0885</v>
       </c>
       <c r="J11" t="n">
-        <v>21.9994</v>
+        <v>21.455</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8173999999999997</v>
+        <v>0.4125999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>21.1817</v>
+        <v>21.042</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.1005</v>
+        <v>-6.752899999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.0193</v>
+        <v>-5.7992</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0813</v>
+        <v>-0.9536999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.4343</v>
+        <v>-10.4712</v>
       </c>
       <c r="Q11" t="n">
-        <v>-34.7057</v>
+        <v>-34.8275</v>
       </c>
       <c r="R11" t="n">
-        <v>24.2711</v>
+        <v>24.3567</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.4866</v>
+        <v>-7.512</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.86</v>
+        <v>-1.8398</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.6268</v>
+        <v>-5.6719</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9513999999999999</v>
+        <v>-0.9408000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>6.4276</v>
+        <v>6.394</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.3791</v>
+        <v>-7.3347</v>
       </c>
     </row>
     <row r="12">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.354299999999999</v>
+        <v>-7.1166</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7001</v>
+        <v>-6.179</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6542000000000001</v>
+        <v>-0.9380000000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4285</v>
+        <v>-2.4544</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6579999999999997</v>
+        <v>-0.1634</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0865</v>
+        <v>-2.2909</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6747000000000001</v>
+        <v>1.204</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1896</v>
+        <v>0.5710999999999998</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4851</v>
+        <v>0.6329</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1032</v>
+        <v>-3.6585</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4683</v>
+        <v>-0.7344999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.5716</v>
+        <v>-2.9238</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805999999999999</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.2587</v>
+        <v>-10.6987</v>
       </c>
       <c r="R12" t="n">
-        <v>6.5782</v>
+        <v>7.2842</v>
       </c>
       <c r="S12" t="n">
-        <v>1.332</v>
+        <v>1.8743</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3731</v>
+        <v>1.8245</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.04109999999999991</v>
+        <v>0.04980000000000009</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.5773</v>
+        <v>-3.1221</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5106</v>
+        <v>1.4913</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.088</v>
+        <v>-4.6134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. PLUMMER</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.3118</v>
+        <v>-8.546900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.987300000000001</v>
+        <v>-19.1631</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.3246</v>
+        <v>10.6164</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.613499999999999</v>
+        <v>-10.1496</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.659699999999999</v>
+        <v>-3.279</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0463</v>
+        <v>-6.8711</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4733999999999998</v>
+        <v>4.5628</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.6311</v>
+        <v>5.937199999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>3.157799999999999</v>
+        <v>-1.3747</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.1402</v>
+        <v>-14.7123</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.0286</v>
+        <v>-9.2163</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1115</v>
+        <v>-5.4961</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1341</v>
+        <v>-12.975</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.3513</v>
+        <v>-63.2817</v>
       </c>
       <c r="R13" t="n">
-        <v>7.4855</v>
+        <v>50.3066</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.4376</v>
+        <v>-7.1727</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0797</v>
+        <v>-3.9818</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.3579</v>
+        <v>-3.1912</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3949</v>
+        <v>21.7501</v>
       </c>
       <c r="W13" t="n">
-        <v>4.917</v>
+        <v>43.5371</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.312</v>
+        <v>-21.7872</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. DUKE JR</t>
+          <t>A. PLUMMER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.207</v>
+        <v>-10.318</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.0611</v>
+        <v>-3.165899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1459</v>
+        <v>-7.152200000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.3773</v>
+        <v>-5.6343</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.218</v>
+        <v>-8.6214</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.1593</v>
+        <v>2.9871</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.0654</v>
+        <v>-0.6198999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8435999999999999</v>
+        <v>-3.6766</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.909</v>
+        <v>3.056699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.312</v>
+        <v>-5.0143</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0616</v>
+        <v>-4.9445</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2502</v>
+        <v>-0.06969999999999998</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0415</v>
+        <v>1.1381</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.6197</v>
+        <v>-6.373699999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>6.578200000000001</v>
+        <v>7.511900000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.6393</v>
+        <v>-4.4509</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4143</v>
+        <v>-1.0748</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2251</v>
+        <v>-3.3761</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8511</v>
+        <v>-1.3711</v>
       </c>
       <c r="W14" t="n">
-        <v>7.0381</v>
+        <v>4.9026</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.187</v>
+        <v>-6.2738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.6082</v>
+        <v>-10.7326</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.179400000000001</v>
+        <v>-16.4356</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.428999999999999</v>
+        <v>5.702900000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.6414</v>
+        <v>-18.9841</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.105700000000001</v>
+        <v>-3.1143</v>
       </c>
       <c r="I15" t="n">
-        <v>-9.5357</v>
+        <v>-15.8698</v>
       </c>
       <c r="J15" t="n">
-        <v>5.023400000000001</v>
+        <v>0.5298999999999996</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5952</v>
+        <v>6.507400000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>1.428000000000001</v>
+        <v>-5.9778</v>
       </c>
       <c r="M15" t="n">
-        <v>-23.6647</v>
+        <v>-19.5139</v>
       </c>
       <c r="N15" t="n">
-        <v>-12.701</v>
+        <v>-9.622</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.964</v>
+        <v>-9.8917</v>
       </c>
       <c r="P15" t="n">
-        <v>29.715</v>
+        <v>12.5199</v>
       </c>
       <c r="Q15" t="n">
-        <v>-18.3734</v>
+        <v>-21.8529</v>
       </c>
       <c r="R15" t="n">
-        <v>48.0886</v>
+        <v>34.3724</v>
       </c>
       <c r="S15" t="n">
-        <v>-14.6214</v>
+        <v>2.5072</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9885000000000002</v>
+        <v>2.1487</v>
       </c>
       <c r="U15" t="n">
-        <v>-13.6333</v>
+        <v>0.3586000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.0604</v>
+        <v>-6.774999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>9.1593</v>
+        <v>2.7386</v>
       </c>
       <c r="X15" t="n">
-        <v>-17.2197</v>
+        <v>-9.513499999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>D. DUKE JR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>-15.1124</v>
+        <v>-11.094</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.128300000000001</v>
+        <v>-4.025399999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.984400000000001</v>
+        <v>-7.0686</v>
       </c>
       <c r="G16" t="n">
-        <v>-16.7313</v>
+        <v>-10.722</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4208999999999998</v>
+        <v>-2.852599999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-17.1522</v>
+        <v>-7.8695</v>
       </c>
       <c r="J16" t="n">
-        <v>1.574</v>
+        <v>-2.6623</v>
       </c>
       <c r="K16" t="n">
-        <v>7.5853</v>
+        <v>2.9134</v>
       </c>
       <c r="L16" t="n">
-        <v>-6.0113</v>
+        <v>-5.5759</v>
       </c>
       <c r="M16" t="n">
-        <v>-18.3051</v>
+        <v>-8.0596</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.164499999999999</v>
+        <v>-5.7657</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.141</v>
+        <v>-2.2938</v>
       </c>
       <c r="P16" t="n">
-        <v>9.980700000000001</v>
+        <v>-6.146</v>
       </c>
       <c r="Q16" t="n">
-        <v>-14.5174</v>
+        <v>-19.3487</v>
       </c>
       <c r="R16" t="n">
-        <v>24.4977</v>
+        <v>13.2025</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4046999999999996</v>
+        <v>2.4417</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4651</v>
+        <v>5.7426</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.8696</v>
+        <v>-3.3005</v>
       </c>
       <c r="V16" t="n">
-        <v>-7.957199999999999</v>
+        <v>3.332</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3499</v>
+        <v>12.2431</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.306999999999999</v>
+        <v>-8.911100000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.468</v>
+        <v>-23.4288</v>
       </c>
       <c r="E17" t="n">
-        <v>-27.7225</v>
+        <v>-22.1832</v>
       </c>
       <c r="F17" t="n">
-        <v>6.2548</v>
+        <v>-1.2456</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.0253</v>
+        <v>-18.0377</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.6014</v>
+        <v>-20.6128</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.423799999999999</v>
+        <v>2.5751</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.507300000000001</v>
+        <v>-6.0929</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7064999999999999</v>
+        <v>-10.2632</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8009</v>
+        <v>4.1703</v>
       </c>
       <c r="M17" t="n">
-        <v>-12.5178</v>
+        <v>-11.9449</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.8948</v>
+        <v>-10.3495</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.6226</v>
+        <v>-1.5956</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.837</v>
+        <v>-10.4711</v>
       </c>
       <c r="Q17" t="n">
-        <v>-54.44</v>
+        <v>-30.5027</v>
       </c>
       <c r="R17" t="n">
-        <v>40.603</v>
+        <v>20.0316</v>
       </c>
       <c r="S17" t="n">
-        <v>-8.7582</v>
+        <v>10.0914</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.3911</v>
+        <v>9.6526</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.3672</v>
+        <v>0.4386999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>16.1523</v>
+        <v>-5.0116</v>
       </c>
       <c r="W17" t="n">
-        <v>33.6161</v>
+        <v>4.7598</v>
       </c>
       <c r="X17" t="n">
-        <v>-17.4637</v>
+        <v>-9.7713</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>-23.3773</v>
+        <v>-24.8561</v>
       </c>
       <c r="E18" t="n">
-        <v>-21.7588</v>
+        <v>-22.4901</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6185</v>
+        <v>-2.3661</v>
       </c>
       <c r="G18" t="n">
-        <v>-17.9678</v>
+        <v>-28.0458</v>
       </c>
       <c r="H18" t="n">
-        <v>-20.4527</v>
+        <v>-15.0254</v>
       </c>
       <c r="I18" t="n">
-        <v>2.484999999999999</v>
+        <v>-13.02</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.7426</v>
+        <v>-2.0768</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.922000000000001</v>
+        <v>0.3117999999999994</v>
       </c>
       <c r="L18" t="n">
-        <v>4.1796</v>
+        <v>-2.3887</v>
       </c>
       <c r="M18" t="n">
-        <v>-12.2249</v>
+        <v>-25.9687</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.5307</v>
+        <v>-15.3375</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6944</v>
+        <v>-10.6311</v>
       </c>
       <c r="P18" t="n">
-        <v>-10.4343</v>
+        <v>33.0065</v>
       </c>
       <c r="Q18" t="n">
-        <v>-30.3958</v>
+        <v>-26.4052</v>
       </c>
       <c r="R18" t="n">
-        <v>19.9612</v>
+        <v>59.4119</v>
       </c>
       <c r="S18" t="n">
-        <v>10.0511</v>
+        <v>-17.476</v>
       </c>
       <c r="T18" t="n">
-        <v>9.5907</v>
+        <v>-3.1251</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4603999999999999</v>
+        <v>-14.3504</v>
       </c>
       <c r="V18" t="n">
-        <v>-5.026299999999999</v>
+        <v>-12.3406</v>
       </c>
       <c r="W18" t="n">
-        <v>4.7888</v>
+        <v>9.117699999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-9.815</v>
+        <v>-21.4583</v>
       </c>
     </row>
     <row r="19">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>-25.3445</v>
+        <v>-28.5389</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.7394</v>
+        <v>-17.5812</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.605</v>
+        <v>-10.9577</v>
       </c>
       <c r="G19" t="n">
-        <v>-13.4009</v>
+        <v>-15.1876</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.98</v>
+        <v>-6.7275</v>
       </c>
       <c r="I19" t="n">
-        <v>-7.421</v>
+        <v>-8.4603</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.306</v>
+        <v>-5.9029</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0643</v>
+        <v>-1.8561</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.2418</v>
+        <v>-4.0469</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.095000000000001</v>
+        <v>-9.2849</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.9156</v>
+        <v>-4.8715</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.1793</v>
+        <v>-4.4133</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1343</v>
+        <v>-1.1383</v>
       </c>
       <c r="Q19" t="n">
-        <v>-8.392799999999999</v>
+        <v>-8.4224</v>
       </c>
       <c r="R19" t="n">
-        <v>7.2586</v>
+        <v>7.2842</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.5501</v>
+        <v>-2.8809</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2733</v>
+        <v>-1.4788</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2771</v>
+        <v>-1.402</v>
       </c>
       <c r="V19" t="n">
-        <v>-8.2593</v>
+        <v>-9.331899999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.7673</v>
+        <v>-1.777</v>
       </c>
       <c r="X19" t="n">
-        <v>-6.491899999999999</v>
+        <v>-7.5549</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>-36.5895</v>
+        <v>-36.2275</v>
       </c>
       <c r="E20" t="n">
-        <v>-37.8113</v>
+        <v>-26.8191</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2219</v>
+        <v>-9.408300000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-10.0981</v>
+        <v>-7.717700000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-8.9678</v>
+        <v>-9.546899999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1302</v>
+        <v>1.829499999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.860799999999999</v>
+        <v>18.9634</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.8198</v>
+        <v>9.865699999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9587999999999999</v>
+        <v>9.097899999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.2371</v>
+        <v>-26.6811</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.148</v>
+        <v>-19.413</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0891</v>
+        <v>-7.2683</v>
       </c>
       <c r="P20" t="n">
-        <v>-12.7026</v>
+        <v>-21.1698</v>
       </c>
       <c r="Q20" t="n">
-        <v>-30.3956</v>
+        <v>-78.9881</v>
       </c>
       <c r="R20" t="n">
-        <v>17.6928</v>
+        <v>57.8184</v>
       </c>
       <c r="S20" t="n">
-        <v>-8.280200000000001</v>
+        <v>-24.9484</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.5155</v>
+        <v>-12.7993</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.7651</v>
+        <v>-12.1488</v>
       </c>
       <c r="V20" t="n">
-        <v>-5.5084</v>
+        <v>17.6085</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9605</v>
+        <v>46.0052</v>
       </c>
       <c r="X20" t="n">
-        <v>-7.4689</v>
+        <v>-28.3966</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>-46.738</v>
+        <v>-45.7928</v>
       </c>
       <c r="E21" t="n">
-        <v>-30.7879</v>
+        <v>-46.231</v>
       </c>
       <c r="F21" t="n">
-        <v>-15.95</v>
+        <v>0.4379</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.256799999999999</v>
+        <v>-7.8284</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9744</v>
+        <v>-8.225300000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7176</v>
+        <v>0.3969999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>25.5721</v>
+        <v>0.5858999999999996</v>
       </c>
       <c r="K21" t="n">
-        <v>9.379300000000001</v>
+        <v>-2.4685</v>
       </c>
       <c r="L21" t="n">
-        <v>16.1925</v>
+        <v>3.054599999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-26.8289</v>
+        <v>-8.4145</v>
       </c>
       <c r="N21" t="n">
-        <v>-12.3537</v>
+        <v>-5.7568</v>
       </c>
       <c r="O21" t="n">
-        <v>-14.4752</v>
+        <v>-2.6573</v>
       </c>
       <c r="P21" t="n">
-        <v>-25.6323</v>
+        <v>-18.6657</v>
       </c>
       <c r="Q21" t="n">
-        <v>-57.6156</v>
+        <v>-43.25</v>
       </c>
       <c r="R21" t="n">
-        <v>31.9835</v>
+        <v>24.5841</v>
       </c>
       <c r="S21" t="n">
-        <v>-18.5954</v>
+        <v>-11.6351</v>
       </c>
       <c r="T21" t="n">
-        <v>-9.318</v>
+        <v>-6.6062</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.277699999999999</v>
+        <v>-5.0288</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2535</v>
+        <v>-7.6637</v>
       </c>
       <c r="W21" t="n">
-        <v>10.5734</v>
+        <v>3.0393</v>
       </c>
       <c r="X21" t="n">
-        <v>-11.8271</v>
+        <v>-10.703</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>-49.366</v>
+        <v>-49.4774</v>
       </c>
       <c r="E22" t="n">
-        <v>-33.6388</v>
+        <v>-37.9839</v>
       </c>
       <c r="F22" t="n">
-        <v>-15.7273</v>
+        <v>-11.4935</v>
       </c>
       <c r="G22" t="n">
-        <v>-14.6215</v>
+        <v>1.3444</v>
       </c>
       <c r="H22" t="n">
-        <v>-13.2143</v>
+        <v>-8.2723</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4072</v>
+        <v>9.616899999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>10.7286</v>
+        <v>31.611</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8607</v>
+        <v>7.315799999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>5.867899999999999</v>
+        <v>24.2947</v>
       </c>
       <c r="M22" t="n">
-        <v>-25.3498</v>
+        <v>-30.2658</v>
       </c>
       <c r="N22" t="n">
-        <v>-18.075</v>
+        <v>-15.5882</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.274900000000001</v>
+        <v>-14.6779</v>
       </c>
       <c r="P22" t="n">
-        <v>-22.6832</v>
+        <v>-26.4055</v>
       </c>
       <c r="Q22" t="n">
-        <v>-67.8232</v>
+        <v>-72.38679999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>45.1398</v>
+        <v>45.9814</v>
       </c>
       <c r="S22" t="n">
-        <v>-21.0735</v>
+        <v>-24.9844</v>
       </c>
       <c r="T22" t="n">
-        <v>-11.3505</v>
+        <v>-12.3328</v>
       </c>
       <c r="U22" t="n">
-        <v>-9.722999999999999</v>
+        <v>-12.6521</v>
       </c>
       <c r="V22" t="n">
-        <v>9.011900000000001</v>
+        <v>0.5678000000000002</v>
       </c>
       <c r="W22" t="n">
-        <v>34.8059</v>
+        <v>15.1246</v>
       </c>
       <c r="X22" t="n">
-        <v>-25.7939</v>
+        <v>-14.5567</v>
       </c>
     </row>
     <row r="23">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>-161.3425</v>
+        <v>-125.8962</v>
       </c>
       <c r="E23" t="n">
-        <v>-119.7501</v>
+        <v>-129.3163</v>
       </c>
       <c r="F23" t="n">
-        <v>-41.5924</v>
+        <v>3.418400000000002</v>
       </c>
       <c r="G23" t="n">
-        <v>-97.2624</v>
+        <v>-93.18610000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-92.50229999999999</v>
+        <v>-101.778</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.7601</v>
+        <v>8.592399999999998</v>
       </c>
       <c r="J23" t="n">
-        <v>153.1108</v>
+        <v>187.04</v>
       </c>
       <c r="K23" t="n">
-        <v>55.8816</v>
+        <v>75.85779999999998</v>
       </c>
       <c r="L23" t="n">
-        <v>97.22889999999998</v>
+        <v>111.1806</v>
       </c>
       <c r="M23" t="n">
-        <v>-250.3723</v>
+        <v>-280.2253</v>
       </c>
       <c r="N23" t="n">
-        <v>-148.3832</v>
+        <v>-177.6367</v>
       </c>
       <c r="O23" t="n">
-        <v>-101.9896</v>
+        <v>-102.5873</v>
       </c>
       <c r="P23" t="n">
-        <v>2.267599999999987</v>
+        <v>13.6572</v>
       </c>
       <c r="Q23" t="n">
-        <v>-491.0947</v>
+        <v>-594.1196</v>
       </c>
       <c r="R23" t="n">
-        <v>493.3614</v>
+        <v>607.7762</v>
       </c>
       <c r="S23" t="n">
-        <v>-67.76179999999999</v>
+        <v>-59.93000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8809000000000022</v>
+        <v>7.514099999999997</v>
       </c>
       <c r="U23" t="n">
-        <v>-68.64439999999999</v>
+        <v>-67.44390000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>1.413800000000001</v>
+        <v>13.5618</v>
       </c>
       <c r="W23" t="n">
-        <v>217.3502</v>
+        <v>270.2491000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-215.9363</v>
+        <v>-256.687</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BAXI Manresa.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BAXI Manresa.xlsx
@@ -565,13 +565,13 @@
         <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>61.475</v>
+        <v>40.3002</v>
       </c>
       <c r="E2" t="n">
-        <v>58.3651</v>
+        <v>40.8149</v>
       </c>
       <c r="F2" t="n">
-        <v>3.109599999999999</v>
+        <v>-0.5143999999999995</v>
       </c>
       <c r="G2" t="n">
         <v>-0.6277999999999992</v>
@@ -610,13 +610,13 @@
         <v>43.7052</v>
       </c>
       <c r="S2" t="n">
-        <v>30.4718</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>24.0227</v>
+        <v>6.472099999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>6.4492</v>
+        <v>2.8251</v>
       </c>
       <c r="V2" t="n">
         <v>24.119</v>
@@ -643,13 +643,13 @@
         <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>29.4268</v>
+        <v>27.6887</v>
       </c>
       <c r="E3" t="n">
-        <v>30.7167</v>
+        <v>26.5442</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2903</v>
+        <v>1.1446</v>
       </c>
       <c r="G3" t="n">
         <v>24.5472</v>
@@ -688,13 +688,13 @@
         <v>46.2095</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8195</v>
+        <v>-3.5575</v>
       </c>
       <c r="T3" t="n">
-        <v>6.4988</v>
+        <v>2.3261</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.318300000000001</v>
+        <v>-5.8839</v>
       </c>
       <c r="V3" t="n">
         <v>-11.5112</v>
@@ -721,13 +721,13 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>24.0078</v>
+        <v>27.2216</v>
       </c>
       <c r="E4" t="n">
-        <v>3.709399999999998</v>
+        <v>12.0781</v>
       </c>
       <c r="F4" t="n">
-        <v>20.2984</v>
+        <v>15.1435</v>
       </c>
       <c r="G4" t="n">
         <v>-12.1798</v>
@@ -766,13 +766,13 @@
         <v>73.297</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.7589</v>
+        <v>-0.5449000000000002</v>
       </c>
       <c r="T4" t="n">
-        <v>-9.960900000000001</v>
+        <v>-1.5924</v>
       </c>
       <c r="U4" t="n">
-        <v>6.201599999999999</v>
+        <v>1.047</v>
       </c>
       <c r="V4" t="n">
         <v>8.9884</v>
@@ -799,13 +799,13 @@
         <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>13.4816</v>
+        <v>17.1658</v>
       </c>
       <c r="E5" t="n">
-        <v>2.693000000000001</v>
+        <v>4.079800000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>10.7885</v>
+        <v>13.0859</v>
       </c>
       <c r="G5" t="n">
         <v>13.3238</v>
@@ -844,13 +844,13 @@
         <v>33.917</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.8194</v>
+        <v>-3.1353</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.4773</v>
+        <v>-1.0904</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.3424</v>
+        <v>-2.0451</v>
       </c>
       <c r="V5" t="n">
         <v>3.7905</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>M. GASPA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>9.026299999999999</v>
+        <v>3.2153</v>
       </c>
       <c r="E6" t="n">
-        <v>6.001600000000001</v>
+        <v>4.731</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0246</v>
+        <v>-1.5157</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.6158</v>
+        <v>1.1571</v>
       </c>
       <c r="H6" t="n">
-        <v>-12.6159</v>
+        <v>3.7871</v>
       </c>
       <c r="I6" t="n">
-        <v>6.000100000000001</v>
+        <v>-2.6298</v>
       </c>
       <c r="J6" t="n">
-        <v>15.9152</v>
+        <v>6.821300000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9477</v>
+        <v>5.1841</v>
       </c>
       <c r="L6" t="n">
-        <v>11.9674</v>
+        <v>1.6374</v>
       </c>
       <c r="M6" t="n">
-        <v>-22.5307</v>
+        <v>-5.6644</v>
       </c>
       <c r="N6" t="n">
-        <v>-16.5639</v>
+        <v>-1.3969</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.966799999999999</v>
+        <v>-4.267</v>
       </c>
       <c r="P6" t="n">
-        <v>12.0646</v>
+        <v>6.3736</v>
       </c>
       <c r="Q6" t="n">
-        <v>-34.3724</v>
+        <v>-3.8697</v>
       </c>
       <c r="R6" t="n">
-        <v>46.4373</v>
+        <v>10.2433</v>
       </c>
       <c r="S6" t="n">
-        <v>9.687099999999999</v>
+        <v>-2.2138</v>
       </c>
       <c r="T6" t="n">
-        <v>13.7635</v>
+        <v>-0.7153</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.0765</v>
+        <v>-1.499</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.1094</v>
+        <v>-2.1016</v>
       </c>
       <c r="W6" t="n">
-        <v>10.6954</v>
+        <v>2.4946</v>
       </c>
       <c r="X6" t="n">
-        <v>-16.8047</v>
+        <v>-4.596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GASPA</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1816</v>
+        <v>2.1602</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6404</v>
+        <v>-1.5018</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4589</v>
+        <v>3.661799999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1571</v>
+        <v>-6.6158</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7871</v>
+        <v>-12.6159</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6298</v>
+        <v>6.000100000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>6.821300000000001</v>
+        <v>15.9152</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1841</v>
+        <v>3.9477</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6374</v>
+        <v>11.9674</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.6644</v>
+        <v>-22.5307</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3969</v>
+        <v>-16.5639</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.267</v>
+        <v>-5.966799999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>6.3736</v>
+        <v>12.0646</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8697</v>
+        <v>-34.3724</v>
       </c>
       <c r="R7" t="n">
-        <v>10.2433</v>
+        <v>46.4373</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.2477</v>
+        <v>2.8204</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8057000000000001</v>
+        <v>6.26</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.4421</v>
+        <v>-3.4394</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1016</v>
+        <v>-6.1094</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4946</v>
+        <v>10.6954</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.596</v>
+        <v>-16.8047</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SANCHEZ</t>
+          <t>H. BENITEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0607</v>
+        <v>1.3969</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8963</v>
+        <v>-5.8437</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1644</v>
+        <v>7.2407</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5462</v>
+        <v>14.7019</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3932</v>
+        <v>-5.3865</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.153</v>
+        <v>20.0885</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6872</v>
+        <v>21.455</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4934</v>
+        <v>0.4125999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1939</v>
+        <v>21.042</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.859</v>
+        <v>-6.752899999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1002</v>
+        <v>-5.7992</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.9536999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6829</v>
+        <v>-10.4712</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-34.8275</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6829</v>
+        <v>24.3567</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1974</v>
+        <v>-1.893</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2091</v>
+        <v>1.1352</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0117</v>
+        <v>-3.0283</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9408000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>6.394</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-7.3347</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2314</v>
+        <v>-0.9318000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9273</v>
+        <v>-1.6904</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6958</v>
+        <v>0.7585999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7667999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.009400000000000006</v>
+        <v>0.2902</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.05119999999999998</v>
+        <v>0.1856</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0418</v>
+        <v>0.1046</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. IZAW-BOLAVIE</t>
+          <t>L. SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8518</v>
+        <v>-0.9736</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5424</v>
+        <v>-0.7779</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3093</v>
+        <v>-0.1957</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7625</v>
+        <v>-1.5462</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2986000000000001</v>
+        <v>-0.3932</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4638</v>
+        <v>-1.153</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0077</v>
+        <v>-0.6872</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.045</v>
+        <v>-0.4934</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0372</v>
+        <v>-0.1939</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7547</v>
+        <v>-0.859</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7463</v>
+        <v>0.1002</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5011</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6830000000000001</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4552</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0908000000000001</v>
+        <v>-0.1103</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6035000000000001</v>
+        <v>-0.0907</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6941999999999999</v>
+        <v>-0.0196</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. BENITEZ</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2218</v>
+        <v>-1.5505</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.818999999999999</v>
+        <v>-13.5682</v>
       </c>
       <c r="F11" t="n">
-        <v>4.597200000000001</v>
+        <v>12.0174</v>
       </c>
       <c r="G11" t="n">
-        <v>14.7019</v>
+        <v>-10.1496</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.3865</v>
+        <v>-3.279</v>
       </c>
       <c r="I11" t="n">
-        <v>20.0885</v>
+        <v>-6.8711</v>
       </c>
       <c r="J11" t="n">
-        <v>21.455</v>
+        <v>4.5628</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4125999999999999</v>
+        <v>5.937199999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>21.042</v>
+        <v>-1.3747</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.752899999999999</v>
+        <v>-14.7123</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.7992</v>
+        <v>-9.2163</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9536999999999999</v>
+        <v>-5.4961</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.4712</v>
+        <v>-12.975</v>
       </c>
       <c r="Q11" t="n">
-        <v>-34.8275</v>
+        <v>-63.2817</v>
       </c>
       <c r="R11" t="n">
-        <v>24.3567</v>
+        <v>50.3066</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.512</v>
+        <v>-0.1762000000000004</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8398</v>
+        <v>1.6136</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.6719</v>
+        <v>-1.7898</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9408000000000001</v>
+        <v>21.7501</v>
       </c>
       <c r="W11" t="n">
-        <v>6.394</v>
+        <v>43.5371</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.3347</v>
+        <v>-21.7872</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. PAULICAP</t>
+          <t>A. IZAW-BOLAVIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1166</v>
+        <v>-3.6354</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.179</v>
+        <v>-2.4203</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9380000000000002</v>
+        <v>-1.2151</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4544</v>
+        <v>-1.7625</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1634</v>
+        <v>-0.2986000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2909</v>
+        <v>-1.4638</v>
       </c>
       <c r="J12" t="n">
-        <v>1.204</v>
+        <v>-1.0077</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5710999999999998</v>
+        <v>-1.045</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6329</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.6585</v>
+        <v>-0.7547</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7344999999999999</v>
+        <v>0.7463</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.9238</v>
+        <v>-1.5011</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4145</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.6987</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>7.2842</v>
+        <v>0.4552</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8743</v>
+        <v>-0.8744999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8245</v>
+        <v>-0.2744</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04980000000000009</v>
+        <v>-0.6001</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.1221</v>
+        <v>-0.3155</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4913</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.6134</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>P. PAULICAP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.546900000000001</v>
+        <v>-7.2174</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.1631</v>
+        <v>-6.561999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>10.6164</v>
+        <v>-0.6555000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-10.1496</v>
+        <v>-2.4544</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.279</v>
+        <v>-0.1634</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.8711</v>
+        <v>-2.2909</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5628</v>
+        <v>1.204</v>
       </c>
       <c r="K13" t="n">
-        <v>5.937199999999999</v>
+        <v>0.5710999999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3747</v>
+        <v>0.6329</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.7123</v>
+        <v>-3.6585</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.2163</v>
+        <v>-0.7344999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.4961</v>
+        <v>-2.9238</v>
       </c>
       <c r="P13" t="n">
-        <v>-12.975</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q13" t="n">
-        <v>-63.2817</v>
+        <v>-10.6987</v>
       </c>
       <c r="R13" t="n">
-        <v>50.3066</v>
+        <v>7.2842</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.1727</v>
+        <v>1.7733</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.9818</v>
+        <v>1.4413</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.1912</v>
+        <v>0.3322000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>21.7501</v>
+        <v>-3.1221</v>
       </c>
       <c r="W13" t="n">
-        <v>43.5371</v>
+        <v>1.4913</v>
       </c>
       <c r="X13" t="n">
-        <v>-21.7872</v>
+        <v>-4.6134</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.318</v>
+        <v>-8.536000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.165899999999999</v>
+        <v>-2.8592</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.152200000000001</v>
+        <v>-5.6769</v>
       </c>
       <c r="G14" t="n">
         <v>-5.6343</v>
@@ -1546,13 +1546,13 @@
         <v>7.511900000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.4509</v>
+        <v>-2.6689</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0748</v>
+        <v>-0.7682</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.3761</v>
+        <v>-1.9007</v>
       </c>
       <c r="V14" t="n">
         <v>-1.3711</v>
@@ -1579,13 +1579,13 @@
         <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>-10.7326</v>
+        <v>-10.4184</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.4356</v>
+        <v>-16.1361</v>
       </c>
       <c r="F15" t="n">
-        <v>5.702900000000001</v>
+        <v>5.717599999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-18.9841</v>
@@ -1624,13 +1624,13 @@
         <v>34.3724</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5072</v>
+        <v>2.8211</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1487</v>
+        <v>2.4484</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3586000000000001</v>
+        <v>0.3730000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-6.774999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.094</v>
+        <v>-12.0107</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.025399999999999</v>
+        <v>-6.637900000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.0686</v>
+        <v>-5.3728</v>
       </c>
       <c r="G16" t="n">
         <v>-10.722</v>
@@ -1702,13 +1702,13 @@
         <v>13.2025</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4417</v>
+        <v>1.5252</v>
       </c>
       <c r="T16" t="n">
-        <v>5.7426</v>
+        <v>3.1298</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.3005</v>
+        <v>-1.6045</v>
       </c>
       <c r="V16" t="n">
         <v>3.332</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>-23.4288</v>
+        <v>-14.4615</v>
       </c>
       <c r="E17" t="n">
-        <v>-22.1832</v>
+        <v>-19.2076</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2456</v>
+        <v>4.7461</v>
       </c>
       <c r="G17" t="n">
-        <v>-18.0377</v>
+        <v>-28.0458</v>
       </c>
       <c r="H17" t="n">
-        <v>-20.6128</v>
+        <v>-15.0254</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5751</v>
+        <v>-13.02</v>
       </c>
       <c r="J17" t="n">
-        <v>-6.0929</v>
+        <v>-2.0768</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.2632</v>
+        <v>0.3117999999999994</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1703</v>
+        <v>-2.3887</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.9449</v>
+        <v>-25.9687</v>
       </c>
       <c r="N17" t="n">
-        <v>-10.3495</v>
+        <v>-15.3375</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5956</v>
+        <v>-10.6311</v>
       </c>
       <c r="P17" t="n">
-        <v>-10.4711</v>
+        <v>33.0065</v>
       </c>
       <c r="Q17" t="n">
-        <v>-30.5027</v>
+        <v>-26.4052</v>
       </c>
       <c r="R17" t="n">
-        <v>20.0316</v>
+        <v>59.4119</v>
       </c>
       <c r="S17" t="n">
-        <v>10.0914</v>
+        <v>-7.0813</v>
       </c>
       <c r="T17" t="n">
-        <v>9.6526</v>
+        <v>0.1570999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4386999999999999</v>
+        <v>-7.2386</v>
       </c>
       <c r="V17" t="n">
-        <v>-5.0116</v>
+        <v>-12.3406</v>
       </c>
       <c r="W17" t="n">
-        <v>4.7598</v>
+        <v>9.117699999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-9.7713</v>
+        <v>-21.4583</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>-24.8561</v>
+        <v>-18.7319</v>
       </c>
       <c r="E18" t="n">
-        <v>-22.4901</v>
+        <v>-14.7718</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3661</v>
+        <v>-3.96</v>
       </c>
       <c r="G18" t="n">
-        <v>-28.0458</v>
+        <v>-7.717700000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-15.0254</v>
+        <v>-9.546899999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-13.02</v>
+        <v>1.829499999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.0768</v>
+        <v>18.9634</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3117999999999994</v>
+        <v>9.865699999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.3887</v>
+        <v>9.097899999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-25.9687</v>
+        <v>-26.6811</v>
       </c>
       <c r="N18" t="n">
-        <v>-15.3375</v>
+        <v>-19.413</v>
       </c>
       <c r="O18" t="n">
-        <v>-10.6311</v>
+        <v>-7.2683</v>
       </c>
       <c r="P18" t="n">
-        <v>33.0065</v>
+        <v>-21.1698</v>
       </c>
       <c r="Q18" t="n">
-        <v>-26.4052</v>
+        <v>-78.9881</v>
       </c>
       <c r="R18" t="n">
-        <v>59.4119</v>
+        <v>57.8184</v>
       </c>
       <c r="S18" t="n">
-        <v>-17.476</v>
+        <v>-7.4527</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.1251</v>
+        <v>-0.7523</v>
       </c>
       <c r="U18" t="n">
-        <v>-14.3504</v>
+        <v>-6.7006</v>
       </c>
       <c r="V18" t="n">
-        <v>-12.3406</v>
+        <v>17.6085</v>
       </c>
       <c r="W18" t="n">
-        <v>9.117699999999999</v>
+        <v>46.0052</v>
       </c>
       <c r="X18" t="n">
-        <v>-21.4583</v>
+        <v>-28.3966</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>-28.5389</v>
+        <v>-26.5989</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.5812</v>
+        <v>-16.7102</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.9577</v>
+        <v>-9.889099999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-15.1876</v>
@@ -1936,13 +1936,13 @@
         <v>7.2842</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.8809</v>
+        <v>-0.9414</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4788</v>
+        <v>-0.6079</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.402</v>
+        <v>-0.3334</v>
       </c>
       <c r="V19" t="n">
         <v>-9.331899999999999</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>-36.2275</v>
+        <v>-28.2821</v>
       </c>
       <c r="E20" t="n">
-        <v>-26.8191</v>
+        <v>-26.9487</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.408300000000001</v>
+        <v>-1.3334</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.717700000000001</v>
+        <v>-18.0377</v>
       </c>
       <c r="H20" t="n">
-        <v>-9.546899999999999</v>
+        <v>-20.6128</v>
       </c>
       <c r="I20" t="n">
-        <v>1.829499999999999</v>
+        <v>2.5751</v>
       </c>
       <c r="J20" t="n">
-        <v>18.9634</v>
+        <v>-6.0929</v>
       </c>
       <c r="K20" t="n">
-        <v>9.865699999999999</v>
+        <v>-10.2632</v>
       </c>
       <c r="L20" t="n">
-        <v>9.097899999999999</v>
+        <v>4.1703</v>
       </c>
       <c r="M20" t="n">
-        <v>-26.6811</v>
+        <v>-11.9449</v>
       </c>
       <c r="N20" t="n">
-        <v>-19.413</v>
+        <v>-10.3495</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.2683</v>
+        <v>-1.5956</v>
       </c>
       <c r="P20" t="n">
-        <v>-21.1698</v>
+        <v>-10.4711</v>
       </c>
       <c r="Q20" t="n">
-        <v>-78.9881</v>
+        <v>-30.5027</v>
       </c>
       <c r="R20" t="n">
-        <v>57.8184</v>
+        <v>20.0316</v>
       </c>
       <c r="S20" t="n">
-        <v>-24.9484</v>
+        <v>5.2384</v>
       </c>
       <c r="T20" t="n">
-        <v>-12.7993</v>
+        <v>4.8869</v>
       </c>
       <c r="U20" t="n">
-        <v>-12.1488</v>
+        <v>0.3513</v>
       </c>
       <c r="V20" t="n">
-        <v>17.6085</v>
+        <v>-5.0116</v>
       </c>
       <c r="W20" t="n">
-        <v>46.0052</v>
+        <v>4.7598</v>
       </c>
       <c r="X20" t="n">
-        <v>-28.3966</v>
+        <v>-9.7713</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>-45.7928</v>
+        <v>-30.3937</v>
       </c>
       <c r="E21" t="n">
-        <v>-46.231</v>
+        <v>-25.5675</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4379</v>
+        <v>-4.826000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.8284</v>
+        <v>1.3444</v>
       </c>
       <c r="H21" t="n">
-        <v>-8.225300000000001</v>
+        <v>-8.2723</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3969999999999999</v>
+        <v>9.616899999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5858999999999996</v>
+        <v>31.611</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.4685</v>
+        <v>7.315799999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>3.054599999999999</v>
+        <v>24.2947</v>
       </c>
       <c r="M21" t="n">
-        <v>-8.4145</v>
+        <v>-30.2658</v>
       </c>
       <c r="N21" t="n">
-        <v>-5.7568</v>
+        <v>-15.5882</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.6573</v>
+        <v>-14.6779</v>
       </c>
       <c r="P21" t="n">
-        <v>-18.6657</v>
+        <v>-26.4055</v>
       </c>
       <c r="Q21" t="n">
-        <v>-43.25</v>
+        <v>-72.38679999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>24.5841</v>
+        <v>45.9814</v>
       </c>
       <c r="S21" t="n">
-        <v>-11.6351</v>
+        <v>-5.9012</v>
       </c>
       <c r="T21" t="n">
-        <v>-6.6062</v>
+        <v>0.0838000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.0288</v>
+        <v>-5.984599999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-7.6637</v>
+        <v>0.5678000000000002</v>
       </c>
       <c r="W21" t="n">
-        <v>3.0393</v>
+        <v>15.1246</v>
       </c>
       <c r="X21" t="n">
-        <v>-10.703</v>
+        <v>-14.5567</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,70 +2122,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>-49.4774</v>
+        <v>-37.7964</v>
       </c>
       <c r="E22" t="n">
-        <v>-37.9839</v>
+        <v>-42.0715</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.4935</v>
+        <v>4.274600000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3444</v>
+        <v>-7.8284</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.2723</v>
+        <v>-8.225300000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>9.616899999999999</v>
+        <v>0.3969999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>31.611</v>
+        <v>0.5858999999999996</v>
       </c>
       <c r="K22" t="n">
-        <v>7.315799999999999</v>
+        <v>-2.4685</v>
       </c>
       <c r="L22" t="n">
-        <v>24.2947</v>
+        <v>3.054599999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-30.2658</v>
+        <v>-8.4145</v>
       </c>
       <c r="N22" t="n">
-        <v>-15.5882</v>
+        <v>-5.7568</v>
       </c>
       <c r="O22" t="n">
-        <v>-14.6779</v>
+        <v>-2.6573</v>
       </c>
       <c r="P22" t="n">
-        <v>-26.4055</v>
+        <v>-18.6657</v>
       </c>
       <c r="Q22" t="n">
-        <v>-72.38679999999999</v>
+        <v>-43.25</v>
       </c>
       <c r="R22" t="n">
-        <v>45.9814</v>
+        <v>24.5841</v>
       </c>
       <c r="S22" t="n">
-        <v>-24.9844</v>
+        <v>-3.6386</v>
       </c>
       <c r="T22" t="n">
-        <v>-12.3328</v>
+        <v>-2.4466</v>
       </c>
       <c r="U22" t="n">
-        <v>-12.6521</v>
+        <v>-1.1921</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5678000000000002</v>
+        <v>-7.6637</v>
       </c>
       <c r="W22" t="n">
-        <v>15.1246</v>
+        <v>3.0393</v>
       </c>
       <c r="X22" t="n">
-        <v>-14.5567</v>
+        <v>-10.703</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>-125.8962</v>
+        <v>-82.3896</v>
       </c>
       <c r="E23" t="n">
-        <v>-129.3163</v>
+        <v>-115.0268</v>
       </c>
       <c r="F23" t="n">
-        <v>3.418400000000002</v>
+        <v>32.6362</v>
       </c>
       <c r="G23" t="n">
         <v>-93.18610000000001</v>
@@ -2218,7 +2218,7 @@
         <v>-101.778</v>
       </c>
       <c r="I23" t="n">
-        <v>8.592399999999998</v>
+        <v>8.5924</v>
       </c>
       <c r="J23" t="n">
         <v>187.04</v>
@@ -2230,7 +2230,7 @@
         <v>111.1806</v>
       </c>
       <c r="M23" t="n">
-        <v>-280.2253</v>
+        <v>-280.2252999999999</v>
       </c>
       <c r="N23" t="n">
         <v>-177.6367</v>
@@ -2239,25 +2239,25 @@
         <v>-102.5873</v>
       </c>
       <c r="P23" t="n">
-        <v>13.6572</v>
+        <v>13.65719999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-594.1196</v>
       </c>
       <c r="R23" t="n">
-        <v>607.7762</v>
+        <v>607.7762000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-59.93000000000001</v>
+        <v>-16.424</v>
       </c>
       <c r="T23" t="n">
-        <v>7.514099999999997</v>
+        <v>21.8017</v>
       </c>
       <c r="U23" t="n">
-        <v>-67.44390000000001</v>
+        <v>-38.2265</v>
       </c>
       <c r="V23" t="n">
-        <v>13.5618</v>
+        <v>13.56180000000001</v>
       </c>
       <c r="W23" t="n">
         <v>270.2491000000001</v>
